--- a/TestData/testData.xlsx
+++ b/TestData/testData.xlsx
@@ -1,37 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B5F1FAF-87EE-4F04-A930-0CDEC982C57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TX\Documents\UiPath\tentabsLib\TestData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>date</t>
   </si>
@@ -133,6 +120,9 @@
   </si>
   <si>
     <t>test00119922@gmail.com</t>
+  </si>
+  <si>
+    <t>dhoni</t>
   </si>
   <si>
     <t>chrome.exe</t>
@@ -183,7 +173,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -197,7 +187,6 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -210,13 +199,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -230,19 +213,11 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -251,10 +226,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -384,6 +359,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -407,10 +383,11 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -419,13 +396,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -501,6 +478,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -520,36 +498,34 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X3"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
-    <col min="13" max="13" width="24.5703125" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.71094" customWidth="1"/>
+    <col min="4" max="4" width="15.85547" customWidth="1"/>
+    <col min="7" max="7" width="35.71094" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578" customWidth="1"/>
+    <col min="11" max="11" width="18.28516" customWidth="1"/>
+    <col min="13" max="13" width="24.57031" customWidth="1"/>
+    <col min="15" max="15" width="17.42578" customWidth="1"/>
+    <col min="18" max="18" width="14.42578" customWidth="1"/>
     <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" customWidth="1"/>
+    <col min="20" max="20" width="12.14063" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85547" customWidth="1"/>
     <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="19.140625" customWidth="1"/>
+    <col min="24" max="24" width="19.14063" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -623,7 +599,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="30.75">
+    <row r="2" ht="45">
       <c r="A2">
         <v>5</v>
       </c>
@@ -664,19 +640,19 @@
         <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q2">
         <v>2003</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2">
         <v>2030</v>
@@ -691,13 +667,13 @@
         <v>321654987</v>
       </c>
       <c r="W2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="30.75">
+    <row r="3" ht="45">
       <c r="A3">
         <v>8</v>
       </c>
@@ -708,7 +684,7 @@
         <v>124536</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>25</v>
@@ -717,40 +693,40 @@
         <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K3" t="s">
         <v>31</v>
       </c>
       <c r="L3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" t="s">
         <v>44</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N3" t="s">
-        <v>43</v>
-      </c>
       <c r="O3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q3">
         <v>2002</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S3">
         <v>2029</v>
@@ -765,16 +741,16 @@
         <v>124548425</v>
       </c>
       <c r="W3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" xr:uid="{2B57A723-2811-4EA9-B67A-C370676C0CBC}"/>
-    <hyperlink ref="M3" r:id="rId2" xr:uid="{4B4A4A29-3525-4052-B588-A0D43C6886D9}"/>
+    <hyperlink ref="M2" r:id="rId1"/>
+    <hyperlink ref="M3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TestData/testData.xlsx
+++ b/TestData/testData.xlsx
@@ -158,7 +158,7 @@
     <t>mrs</t>
   </si>
   <si>
-    <t>test00112233@gmail.com</t>
+    <t>test001122314yoglyo4@gmail.com</t>
   </si>
   <si>
     <t>msedge.exe</t>
@@ -167,7 +167,16 @@
     <t>May</t>
   </si>
   <si>
-    <t>thsirt</t>
+    <t>tshirt</t>
+  </si>
+  <si>
+    <t>test0011443344@gmail.com</t>
+  </si>
+  <si>
+    <t>Sanju</t>
+  </si>
+  <si>
+    <t>dress</t>
   </si>
 </sst>
 </file>
@@ -747,6 +756,50 @@
         <v>39</v>
       </c>
     </row>
+    <row r="4">
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4">
+        <v>2003</v>
+      </c>
+      <c r="R4" t="s">
+        <v>52</v>
+      </c>
+      <c r="S4">
+        <v>2030</v>
+      </c>
+      <c r="T4">
+        <v>2</v>
+      </c>
+      <c r="U4">
+        <v>123</v>
+      </c>
+      <c r="V4">
+        <v>321654987</v>
+      </c>
+      <c r="W4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X4" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
